--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ba4fe86b9db4a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R6acb0497a19f45df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R22934f91640b4dd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rde10b1bb537e4b7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R77752be192f94575"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R565db36e800d489a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -63,9 +63,6 @@
     <x:t xml:space="preserve">3D printing filament</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Bambu PLA Basic; for the silicone casting mold</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Mold release agent</x:t>
   </x:si>
   <x:si>
@@ -76,9 +73,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Gray silicone coating ink</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Custom coolgray; dry at room temperature ~8 h or with 100°C hot air ~10 min</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://item.taobao.com/item.htm?id=594951473152</x:t>
@@ -486,8 +480,8 @@
       <x:c r="A7" s="6" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>17</x:v>
+      <x:c r="B7" s="6" t="str">
+        <x:v>Bambu PLA Basic; for the silicone casting mold and sensor structural parts</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
         <x:v>https://e.tb.cn/h.8yFoHAKwVr1shmb?tk=97oXTMkPX9c</x:v>
@@ -495,46 +489,46 @@
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
       <x:c r="A8" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="s">
+      <x:c r="C8" s="7" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="8" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>Custom coolgray; dry at room temperature ~8 h; a heat gun can accelerate drying</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
       <x:c r="A10" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
       <x:c r="A11" s="8" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1"/>
@@ -560,7 +554,7 @@
     <x:mergeCell ref="A13:C14"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="R366d693df850478d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="Rf2d4fd5409c54d3b"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rde10b1bb537e4b7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R77752be192f94575"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="R565db36e800d489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fb1345e917d4820"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rdcc0c84e3bbf41f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="Rc4657bbf7f3c4bd2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,9 +52,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">LEDs (strip segment)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2.6 mm-wide strip; 8 LEDs per sensor; three illumination directions use red, green and blue</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://item.taobao.com/item.htm?id=570411659913</x:t>
@@ -469,16 +466,16 @@
       <x:c r="A6" s="6" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="s">
+      <x:c r="B6" s="6" t="str">
+        <x:v>2.6 mm RGB strip; 8 LEDs in assembly; 10 firmware positions, final 2 blue optional</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="44" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
         <x:v>Bambu PLA Basic; for the silicone casting mold and sensor structural parts</x:v>
@@ -489,46 +486,46 @@
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
       <x:c r="A8" s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="s">
+      <x:c r="C8" s="7" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="8" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
         <x:v>Custom coolgray; dry at room temperature ~8 h; a heat gun can accelerate drying</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
       <x:c r="A10" s="8" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
       <x:c r="A11" s="8" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="s">
+      <x:c r="C11" s="7" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1"/>
@@ -554,7 +551,7 @@
     <x:mergeCell ref="A13:C14"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="Rf2d4fd5409c54d3b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="R0563db85f3414d33"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
